--- a/data/trans_dic/P19D_R2-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P19D_R2-Edad-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>89,48%</t>
+          <t>90,58%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>92,08%</t>
+          <t>93,07%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>92,98; 97,48</t>
+          <t>93,38; 97,45</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>86,0; 92,45</t>
+          <t>85,54; 91,94</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>84,13; 91,31</t>
+          <t>84,54; 91,49</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>82,18; 94,64</t>
+          <t>83,9; 94,99</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>90,11; 95,39</t>
+          <t>90,26; 95,19</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>83,54; 90,67</t>
+          <t>83,64; 90,54</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>82,62; 89,4</t>
+          <t>82,12; 89,49</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>90,65; 97,93</t>
+          <t>91,81; 98,03</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>92,49; 95,93</t>
+          <t>92,53; 95,79</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>85,78; 90,58</t>
+          <t>85,68; 90,5</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>84,58; 89,75</t>
+          <t>84,62; 89,59</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>86,93; 95,24</t>
+          <t>89,12; 95,66</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>93,39%</t>
+          <t>93,27%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>94,84%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>94,08%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>94,68; 97,89</t>
+          <t>94,53; 97,92</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>88,54; 93,56</t>
+          <t>88,37; 93,35</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>90,77; 95,36</t>
+          <t>90,37; 95,29</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>89,39; 96,35</t>
+          <t>89,03; 95,82</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>91,54; 95,81</t>
+          <t>91,28; 95,71</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>85,16; 90,78</t>
+          <t>84,95; 90,33</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>86,43; 91,89</t>
+          <t>86,36; 91,97</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>93,41; 97,53</t>
+          <t>92,68; 96,69</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>93,96; 96,57</t>
+          <t>93,72; 96,44</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>87,63; 91,24</t>
+          <t>87,64; 91,36</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>89,48; 92,93</t>
+          <t>89,51; 93,04</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>92,29; 96,48</t>
+          <t>91,88; 95,77</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>93,08%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,05%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>90,21; 94,88</t>
+          <t>89,98; 94,8</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>85,98; 91,48</t>
+          <t>85,77; 91,35</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>90,18; 94,61</t>
+          <t>90,23; 94,7</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>91,45; 95,83</t>
+          <t>90,89; 95,18</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>92,42; 96,11</t>
+          <t>92,2; 96,09</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>90,09; 94,38</t>
+          <t>90,21; 94,39</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>91,54; 95,8</t>
+          <t>91,53; 95,61</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>93,61; 96,66</t>
+          <t>93,3; 96,36</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>92,01; 95,03</t>
+          <t>92,09; 94,93</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>89,08; 92,46</t>
+          <t>89,1; 92,54</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>91,7; 94,82</t>
+          <t>91,45; 94,62</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>93,16; 95,78</t>
+          <t>92,75; 95,38</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>66,64%</t>
+          <t>92,26%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>79,8%</t>
+          <t>94,24%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>89,2; 94,64</t>
+          <t>89,37; 94,73</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>83,23; 89,52</t>
+          <t>83,27; 89,73</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>85,17; 91,12</t>
+          <t>84,87; 91,11</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>31,25; 93,53</t>
+          <t>89,88; 94,1</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>89,98; 95,1</t>
+          <t>90,21; 95,11</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,42; 93,64</t>
+          <t>88,76; 93,85</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,6; 95,12</t>
+          <t>90,77; 95,06</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>93,39; 97,22</t>
+          <t>94,89; 97,13</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>90,81; 94,31</t>
+          <t>90,66; 94,21</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>86,95; 91,01</t>
+          <t>86,99; 91,07</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>88,93; 92,64</t>
+          <t>88,99; 92,63</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>50,26; 95,11</t>
+          <t>93,05; 95,4</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>91,69%</t>
+          <t>90,91%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>94,08%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>92,95%</t>
+          <t>92,5%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>83,34; 91,54</t>
+          <t>83,3; 91,55</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>77,92; 85,88</t>
+          <t>77,7; 85,91</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>86,73; 93,1</t>
+          <t>87,02; 93,29</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>89,38; 93,5</t>
+          <t>88,39; 93,1</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>88,03; 94,56</t>
+          <t>88,88; 95,12</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>87,09; 93,55</t>
+          <t>87,02; 93,38</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>89,9; 95,32</t>
+          <t>89,47; 95,16</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>92,61; 95,63</t>
+          <t>92,36; 95,39</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>87,63; 92,55</t>
+          <t>87,4; 92,33</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>83,63; 88,91</t>
+          <t>83,6; 88,7</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>89,35; 93,39</t>
+          <t>89,18; 93,34</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>91,56; 94,1</t>
+          <t>90,97; 93,71</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>89,3%</t>
+          <t>88,83%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>94,73%</t>
+          <t>91,97%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>92,71%</t>
+          <t>90,47%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>83,7; 92,47</t>
+          <t>84,15; 92,62</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>72,74; 83,18</t>
+          <t>71,83; 82,96</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>84,35; 92,54</t>
+          <t>84,29; 92,64</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>86,52; 91,73</t>
+          <t>86,0; 91,23</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>85,92; 93,07</t>
+          <t>85,9; 93,1</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>83,26; 90,87</t>
+          <t>83,11; 90,97</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>86,39; 93,64</t>
+          <t>86,14; 93,19</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>91,48; 98,11</t>
+          <t>89,88; 93,69</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>86,69; 92,02</t>
+          <t>86,66; 92,02</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>79,42; 85,88</t>
+          <t>79,42; 86,03</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>86,84; 92,05</t>
+          <t>86,67; 92,03</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>90,19; 96,22</t>
+          <t>88,67; 91,9</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>89,41%</t>
+          <t>89,65%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>90,37%</t>
+          <t>90,23%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>89,98%</t>
+          <t>89,99%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>77,33; 90,51</t>
+          <t>77,5; 91,01</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>67,71; 81,75</t>
+          <t>68,23; 81,94</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>87,15; 95,1</t>
+          <t>87,29; 95,1</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>85,91; 92,04</t>
+          <t>86,33; 92,21</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>87,48; 95,6</t>
+          <t>87,55; 95,52</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>75,78; 85,04</t>
+          <t>76,4; 85,41</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>82,97; 92,41</t>
+          <t>81,98; 92,3</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>88,28; 92,28</t>
+          <t>88,03; 92,16</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>85,76; 92,64</t>
+          <t>85,57; 92,48</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>75,18; 82,62</t>
+          <t>74,82; 82,9</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>85,69; 92,53</t>
+          <t>85,65; 92,22</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>88,14; 91,76</t>
+          <t>88,41; 91,73</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>85,11%</t>
+          <t>91,48%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>94,18%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>90,05%</t>
+          <t>92,87%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>91,65; 93,72</t>
+          <t>91,57; 93,62</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>85,06; 87,7</t>
+          <t>84,89; 87,56</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>89,4; 91,77</t>
+          <t>89,51; 91,77</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>63,3; 92,13</t>
+          <t>90,32; 92,44</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>92,04; 93,99</t>
+          <t>91,98; 93,93</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>87,88; 90,11</t>
+          <t>87,81; 90,07</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>90,05; 92,15</t>
+          <t>90,06; 92,17</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>93,78; 95,73</t>
+          <t>93,44; 94,81</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>92,14; 93,52</t>
+          <t>92,12; 93,6</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>86,92; 88,65</t>
+          <t>86,78; 88,58</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>90,17; 91,64</t>
+          <t>90,02; 91,61</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>78,5; 93,64</t>
+          <t>92,17; 93,49</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>340157</t>
+          <t>340398</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>287913</t>
+          <t>326914</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>628070</t>
+          <t>667313</t>
         </is>
       </c>
     </row>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>334185; 350348</t>
+          <t>335612; 350246</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>326903; 351408</t>
+          <t>325168; 349474</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>296831; 322171</t>
+          <t>298280; 322826</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>312428; 359777</t>
+          <t>315298; 356956</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>339039; 358914</t>
+          <t>339599; 358151</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>308298; 334642</t>
+          <t>308666; 334161</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>290756; 314635</t>
+          <t>289002; 314952</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>273698; 295660</t>
+          <t>313274; 334492</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>680382; 705745</t>
+          <t>680669; 704665</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>642612; 678601</t>
+          <t>641890; 677981</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>596085; 632543</t>
+          <t>596399; 631428</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>592959; 649643</t>
+          <t>638967; 685909</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>377274</t>
+          <t>417360</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>479352</t>
+          <t>458048</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>856626</t>
+          <t>875408</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>546547; 565082</t>
+          <t>545709; 565282</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>525426; 555244</t>
+          <t>524420; 554014</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>447544; 470211</t>
+          <t>445599; 469857</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>361133; 389235</t>
+          <t>398372; 428774</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>501351; 524733</t>
+          <t>499937; 524222</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>476747; 508249</t>
+          <t>475567; 505692</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>429331; 456443</t>
+          <t>428946; 456830</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>467396; 488007</t>
+          <t>447601; 466996</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1057043; 1086459</t>
+          <t>1054355; 1084958</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1010693; 1052317</t>
+          <t>1010742; 1053632</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>885711; 919833</t>
+          <t>885979; 920901</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>834604; 872506</t>
+          <t>854888; 891127</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>492991</t>
+          <t>557780</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>506149</t>
+          <t>575534</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>999140</t>
+          <t>1133314</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>453695; 477197</t>
+          <t>452531; 476794</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>503303; 535515</t>
+          <t>502095; 534739</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>501312; 525926</t>
+          <t>501608; 526456</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>479908; 502897</t>
+          <t>544653; 570379</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>557808; 580056</t>
+          <t>556506; 579975</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>592400; 620607</t>
+          <t>593202; 620662</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>524584; 548998</t>
+          <t>524514; 547942</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>497575; 513775</t>
+          <t>565123; 583675</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1018088; 1051478</t>
+          <t>1018961; 1050391</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1107299; 1149195</t>
+          <t>1107519; 1150284</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1035215; 1070516</t>
+          <t>1032492; 1068255</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>984077; 1011776</t>
+          <t>1117572; 1149247</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>575028</t>
+          <t>625631</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>674438</t>
+          <t>696305</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1249466</t>
+          <t>1321936</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>361035; 383047</t>
+          <t>361730; 383419</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>449227; 483133</t>
+          <t>449398; 484263</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>436371; 466877</t>
+          <t>434826; 466831</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>269649; 806989</t>
+          <t>609471; 638120</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>395168; 417656</t>
+          <t>396168; 417729</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>496230; 525511</t>
+          <t>498122; 526693</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>493651; 518309</t>
+          <t>494607; 517978</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>656369; 683266</t>
+          <t>687550; 703785</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>766365; 795886</t>
+          <t>765112; 795095</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>957298; 1002008</t>
+          <t>957715; 1002648</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>940200; 979429</t>
+          <t>940808; 979364</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>786839; 1489066</t>
+          <t>1305208; 1338155</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>503128</t>
+          <t>541339</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>504201</t>
+          <t>560512</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1007329</t>
+          <t>1101851</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>226978; 249298</t>
+          <t>226868; 249322</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>282380; 311254</t>
+          <t>281596; 311339</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>321782; 345411</t>
+          <t>322833; 346098</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>490449; 513058</t>
+          <t>526304; 554327</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>280903; 301731</t>
+          <t>283608; 303515</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>341070; 366368</t>
+          <t>340785; 365702</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>355873; 377356</t>
+          <t>354186; 376714</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>495471; 511589</t>
+          <t>550292; 568364</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>518246; 547355</t>
+          <t>516896; 546081</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>630644; 670426</t>
+          <t>630367; 668817</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>685170; 716220</t>
+          <t>683907; 715768</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>992189; 1019771</t>
+          <t>1083637; 1116261</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>318987</t>
+          <t>351093</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>569479</t>
+          <t>396115</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>888465</t>
+          <t>747208</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>178779; 197523</t>
+          <t>179749; 197845</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>190198; 217516</t>
+          <t>187841; 216929</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>194121; 212951</t>
+          <t>193973; 213178</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>309032; 327662</t>
+          <t>339921; 360578</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>212169; 229819</t>
+          <t>212122; 229908</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>249499; 272308</t>
+          <t>249030; 272606</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>239258; 259331</t>
+          <t>238555; 258101</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>549933; 589824</t>
+          <t>387107; 403535</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>399240; 423792</t>
+          <t>399094; 423797</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>445674; 481935</t>
+          <t>445638; 482765</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>440348; 466773</t>
+          <t>439471; 466643</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>864346; 922152</t>
+          <t>732401; 759025</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>247284</t>
+          <t>272269</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>370703</t>
+          <t>403711</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>617987</t>
+          <t>675981</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>98027; 114736</t>
+          <t>98246; 115370</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>125219; 151171</t>
+          <t>126180; 151538</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>128166; 139857</t>
+          <t>128371; 139857</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>237612; 254568</t>
+          <t>262176; 280038</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>182138; 199054</t>
+          <t>182283; 198871</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>230736; 258943</t>
+          <t>232638; 260064</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>188017; 209404</t>
+          <t>185774; 209167</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>362124; 378521</t>
+          <t>393884; 412350</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>287262; 310320</t>
+          <t>286626; 309783</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>367945; 404337</t>
+          <t>366199; 405701</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>320177; 345769</t>
+          <t>320052; 344602</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>605338; 630193</t>
+          <t>664086; 689060</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2854849</t>
+          <t>3105870</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>3392236</t>
+          <t>3417140</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>6247085</t>
+          <t>6523010</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>2251886; 2302857</t>
+          <t>2249837; 2300234</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>2473137; 2549828</t>
+          <t>2468125; 2545943</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2380281; 2443382</t>
+          <t>2383071; 2443180</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2123195; 3090183</t>
+          <t>3066293; 3138379</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>2522663; 2576218</t>
+          <t>2521152; 2574645</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2762378; 2832521</t>
+          <t>2760393; 2831392</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>2580896; 2641074</t>
+          <t>2581069; 2641585</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>3360304; 3429908</t>
+          <t>3390242; 3440254</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>4789258; 4861204</t>
+          <t>4788556; 4865565</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>5259369; 5364415</t>
+          <t>5250889; 5360122</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>4985241; 5066508</t>
+          <t>4976550; 5064315</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>5446122; 6496025</t>
+          <t>6473295; 6566293</t>
         </is>
       </c>
     </row>
